--- a/데이터/graduation_requirements_2024.xlsx
+++ b/데이터/graduation_requirements_2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\AI융개_팀플\데이터\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B9D04F-E8FD-4979-AB2D-F350EDAE2AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E168A42C-14A3-4D92-B2CB-7FD9F21062B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -94,9 +94,6 @@
     <t>융합보안공학과</t>
   </si>
   <si>
-    <t>청정융합에너지공학과</t>
-  </si>
-  <si>
     <t>일반화학 Ⅰ;일반화학 Ⅱ;일반물리학 Ⅰ</t>
   </si>
   <si>
@@ -122,6 +119,10 @@
   </si>
   <si>
     <t>학과</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>청정신소재공학과</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -140,6 +141,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -177,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -188,27 +190,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -233,13 +222,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="시트1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -502,7 +507,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -687,8 +692,8 @@
       </c>
     </row>
     <row r="4" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>24</v>
+      <c r="A4" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="B4" s="2">
         <v>15</v>
@@ -712,7 +717,7 @@
         <v>21</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J4" s="2">
         <v>27</v>
@@ -750,7 +755,7 @@
     </row>
     <row r="5" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2">
         <v>15</v>
@@ -774,7 +779,7 @@
         <v>21</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J5" s="2">
         <v>27</v>
@@ -812,7 +817,7 @@
     </row>
     <row r="6" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6" s="2">
         <v>15</v>
@@ -836,7 +841,7 @@
         <v>21</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J6" s="2">
         <v>27</v>
@@ -874,7 +879,7 @@
     </row>
     <row r="7" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" s="2">
         <v>15</v>
@@ -936,7 +941,7 @@
     </row>
     <row r="8" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="2">
         <v>15</v>
@@ -998,7 +1003,7 @@
     </row>
     <row r="9" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="2">
         <v>15</v>
@@ -1022,7 +1027,7 @@
         <v>21</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J9" s="2">
         <v>27</v>
